--- a/results/ref_threshold_sensitivity/tables/MaxRel_threshold_metrics.xlsx
+++ b/results/ref_threshold_sensitivity/tables/MaxRel_threshold_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,25 +486,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4540647766946757</v>
+        <v>0.4540647766946753</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.09187044661064858</v>
+        <v>-0.09187044661064947</v>
       </c>
       <c r="F2" t="n">
-        <v>0.831719144160682</v>
+        <v>0.8317191441606815</v>
       </c>
       <c r="G2" t="n">
         <v>0.663</v>
       </c>
       <c r="H2" t="n">
-        <v>155.8593159772077</v>
+        <v>155.8593159772076</v>
       </c>
       <c r="I2" t="n">
         <v>343.25348271181</v>
       </c>
       <c r="J2" t="n">
-        <v>9.152322810631688</v>
+        <v>9.152322810631675</v>
       </c>
     </row>
     <row r="3">
@@ -518,10 +518,10 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3375533790435991</v>
+        <v>0.337553379043599</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006330068565398639</v>
+        <v>0.006330068565398417</v>
       </c>
       <c r="F3" t="n">
         <v>1.019111180780905</v>
@@ -550,10 +550,10 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2690628190827336</v>
+        <v>0.2690628190827337</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008013825897995486</v>
+        <v>0.008013825897995597</v>
       </c>
       <c r="F4" t="n">
         <v>1.030698551257481</v>
@@ -562,13 +562,13 @@
         <v>0.45</v>
       </c>
       <c r="H4" t="n">
-        <v>148.9924651300704</v>
+        <v>148.9924651300705</v>
       </c>
       <c r="I4" t="n">
         <v>553.7460197510866</v>
       </c>
       <c r="J4" t="n">
-        <v>4.669555028397693</v>
+        <v>4.669555028397697</v>
       </c>
     </row>
     <row r="5">
@@ -582,25 +582,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2490882289063758</v>
+        <v>0.2490882289063756</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05147986809226424</v>
+        <v>0.05147986809226401</v>
       </c>
       <c r="F5" t="n">
-        <v>1.26051462539427</v>
+        <v>1.260514625394269</v>
       </c>
       <c r="G5" t="n">
         <v>0.173</v>
       </c>
       <c r="H5" t="n">
-        <v>177.0048403230227</v>
+        <v>177.0048403230225</v>
       </c>
       <c r="I5" t="n">
         <v>710.6110196381584</v>
       </c>
       <c r="J5" t="n">
-        <v>3.981816140151961</v>
+        <v>3.981816140151957</v>
       </c>
     </row>
     <row r="6">
@@ -614,25 +614,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2290282931613526</v>
+        <v>0.2290282931613529</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06840918756996783</v>
+        <v>0.06840918756996806</v>
       </c>
       <c r="F6" t="n">
-        <v>1.42590940422742</v>
+        <v>1.425909404227422</v>
       </c>
       <c r="G6" t="n">
         <v>0.082</v>
       </c>
       <c r="H6" t="n">
-        <v>187.9845131799058</v>
+        <v>187.9845131799059</v>
       </c>
       <c r="I6" t="n">
         <v>820.7916610873438</v>
       </c>
       <c r="J6" t="n">
-        <v>3.660958835599072</v>
+        <v>3.660958835599077</v>
       </c>
     </row>
     <row r="7">
@@ -664,7 +664,7 @@
         <v>885.4275528238688</v>
       </c>
       <c r="J7" t="n">
-        <v>3.447740269724833</v>
+        <v>3.447740269724831</v>
       </c>
     </row>
     <row r="8">
@@ -678,25 +678,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2041629597528988</v>
+        <v>0.2041629597528989</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08358159001848942</v>
+        <v>0.08358159001848953</v>
       </c>
       <c r="F8" t="n">
-        <v>1.693155088572846</v>
+        <v>1.693155088572847</v>
       </c>
       <c r="G8" t="n">
         <v>0.026</v>
       </c>
       <c r="H8" t="n">
-        <v>194.4687604532767</v>
+        <v>194.4687604532768</v>
       </c>
       <c r="I8" t="n">
         <v>952.5173454021478</v>
       </c>
       <c r="J8" t="n">
-        <v>3.037457404256477</v>
+        <v>3.037457404256481</v>
       </c>
     </row>
     <row r="9">
@@ -710,25 +710,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2171090769975937</v>
+        <v>0.2171090769975938</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1140971134446456</v>
+        <v>0.1140971134446457</v>
       </c>
       <c r="F9" t="n">
-        <v>2.107610315436805</v>
+        <v>2.107610315436806</v>
       </c>
       <c r="G9" t="n">
         <v>0.005</v>
       </c>
       <c r="H9" t="n">
-        <v>237.7647795625751</v>
+        <v>237.7647795625752</v>
       </c>
       <c r="I9" t="n">
         <v>1095.139746576373</v>
       </c>
       <c r="J9" t="n">
-        <v>3.535853256994267</v>
+        <v>3.535853256994268</v>
       </c>
     </row>
     <row r="10">
@@ -742,25 +742,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2164837485069394</v>
+        <v>0.2164837485069393</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1232080042815751</v>
+        <v>0.123208004281575</v>
       </c>
       <c r="F10" t="n">
-        <v>2.320900790498022</v>
+        <v>2.320900790498021</v>
       </c>
       <c r="G10" t="n">
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>265.8135459136411</v>
+        <v>265.813545913641</v>
       </c>
       <c r="I10" t="n">
         <v>1227.868363084633</v>
       </c>
       <c r="J10" t="n">
-        <v>3.467782559166386</v>
+        <v>3.467782559166384</v>
       </c>
     </row>
     <row r="11">
@@ -774,25 +774,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2491154112060492</v>
+        <v>0.2491154112060493</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1692340719726502</v>
+        <v>0.1692340719726503</v>
       </c>
       <c r="F11" t="n">
-        <v>3.118568286370092</v>
+        <v>3.118568286370094</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>355.8637443138059</v>
+        <v>355.863744313806</v>
       </c>
       <c r="I11" t="n">
         <v>1428.509551420176</v>
       </c>
       <c r="J11" t="n">
-        <v>4.898928794356262</v>
+        <v>4.898928794356264</v>
       </c>
     </row>
     <row r="12">
@@ -824,7 +824,7 @@
         <v>1587.411905297559</v>
       </c>
       <c r="J12" t="n">
-        <v>5.421913695254554</v>
+        <v>5.421913695254558</v>
       </c>
     </row>
     <row r="13">
@@ -838,25 +838,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2596740034226861</v>
+        <v>0.2596740034226862</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1935734680139974</v>
+        <v>0.1935734680139976</v>
       </c>
       <c r="F13" t="n">
-        <v>3.92847050053626</v>
+        <v>3.928470500536262</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>450.9244023184472</v>
+        <v>450.9244023184474</v>
       </c>
       <c r="I13" t="n">
         <v>1736.501907680192</v>
       </c>
       <c r="J13" t="n">
-        <v>5.542146240870012</v>
+        <v>5.542146240870014</v>
       </c>
     </row>
     <row r="14">
@@ -870,25 +870,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2286852390593463</v>
+        <v>0.2286852390593461</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1654627176707681</v>
+        <v>0.1654627176707678</v>
       </c>
       <c r="F14" t="n">
-        <v>3.617148352148144</v>
+        <v>3.617148352148141</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>423.7689487047987</v>
+        <v>423.7689487047983</v>
       </c>
       <c r="I14" t="n">
         <v>1853.066470087412</v>
       </c>
       <c r="J14" t="n">
-        <v>4.831600427020528</v>
+        <v>4.831600427020523</v>
       </c>
     </row>
     <row r="15">
@@ -902,25 +902,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2007699431303814</v>
+        <v>0.2007699431303815</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1402222115493497</v>
+        <v>0.1402222115493499</v>
       </c>
       <c r="F15" t="n">
-        <v>3.315895375232822</v>
+        <v>3.315895375232826</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>400.7771584283191</v>
+        <v>400.7771584283195</v>
       </c>
       <c r="I15" t="n">
         <v>1996.200985961587</v>
       </c>
       <c r="J15" t="n">
-        <v>4.300665574403078</v>
+        <v>4.300665574403083</v>
       </c>
     </row>
     <row r="16">
@@ -934,25 +934,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2008168961751942</v>
+        <v>0.2008168961751941</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1437323887591367</v>
+        <v>0.1437323887591366</v>
       </c>
       <c r="F16" t="n">
-        <v>3.517887869497593</v>
+        <v>3.51788786949759</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>429.6952753753983</v>
+        <v>429.6952753753981</v>
       </c>
       <c r="I16" t="n">
         <v>2139.736663395737</v>
       </c>
       <c r="J16" t="n">
-        <v>4.405752670014368</v>
+        <v>4.405752670014369</v>
       </c>
     </row>
     <row r="17">
@@ -966,25 +966,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1794150350020619</v>
+        <v>0.179415035002062</v>
       </c>
       <c r="E17" t="n">
-        <v>0.124709370668866</v>
+        <v>0.1247093706688661</v>
       </c>
       <c r="F17" t="n">
-        <v>3.279642742464446</v>
+        <v>3.279642742464448</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>407.3769694764212</v>
+        <v>407.3769694764215</v>
       </c>
       <c r="I17" t="n">
         <v>2270.584343568194</v>
       </c>
       <c r="J17" t="n">
-        <v>3.907193209204038</v>
+        <v>3.907193209204044</v>
       </c>
     </row>
     <row r="18">
@@ -998,25 +998,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.177950035566393</v>
+        <v>0.1779500355663928</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1265719127892926</v>
+        <v>0.1265719127892924</v>
       </c>
       <c r="F18" t="n">
-        <v>3.463537123347496</v>
+        <v>3.463537123347494</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>423.0218300961287</v>
+        <v>423.0218300961284</v>
       </c>
       <c r="I18" t="n">
         <v>2377.19441162067</v>
       </c>
       <c r="J18" t="n">
-        <v>3.87588015521672</v>
+        <v>3.875880155216719</v>
       </c>
     </row>
     <row r="19">
@@ -1030,25 +1030,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1801093091118438</v>
+        <v>0.1801093091118439</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1313062917970725</v>
+        <v>0.1313062917970728</v>
       </c>
       <c r="F19" t="n">
-        <v>3.690536344303656</v>
+        <v>3.690536344303659</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>444.3413602864084</v>
+        <v>444.3413602864088</v>
       </c>
       <c r="I19" t="n">
         <v>2467.064931166232</v>
       </c>
       <c r="J19" t="n">
-        <v>3.990592698089621</v>
+        <v>3.990592698089626</v>
       </c>
     </row>
     <row r="20">
@@ -1062,19 +1062,19 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1812893623035286</v>
+        <v>0.1812893623035288</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1352943826576596</v>
+        <v>0.1352943826576597</v>
       </c>
       <c r="F20" t="n">
-        <v>3.941503261863282</v>
+        <v>3.941503261863284</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>471.4850423811629</v>
+        <v>471.4850423811632</v>
       </c>
       <c r="I20" t="n">
         <v>2600.731981128414</v>
@@ -1094,25 +1094,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1748967880624036</v>
+        <v>0.1748967880624035</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1310083193423187</v>
+        <v>0.1310083193423186</v>
       </c>
       <c r="F21" t="n">
-        <v>3.98502825828518</v>
+        <v>3.985028258285178</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>482.4602509001278</v>
+        <v>482.4602509001276</v>
       </c>
       <c r="I21" t="n">
         <v>2758.542659616967</v>
       </c>
       <c r="J21" t="n">
-        <v>3.915466250254441</v>
+        <v>3.915466250254436</v>
       </c>
     </row>
     <row r="22">
@@ -1126,25 +1126,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1693897411386434</v>
+        <v>0.1693897411386435</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1270116667069415</v>
+        <v>0.1270116667069416</v>
       </c>
       <c r="F22" t="n">
-        <v>3.997108018950658</v>
+        <v>3.99710801895066</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>480.3095104593776</v>
+        <v>480.3095104593779</v>
       </c>
       <c r="I22" t="n">
         <v>2835.528924188215</v>
       </c>
       <c r="J22" t="n">
-        <v>3.734636310543173</v>
+        <v>3.734636310543169</v>
       </c>
     </row>
     <row r="23">
@@ -1158,25 +1158,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1719684363777777</v>
+        <v>0.1719684363777775</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1317727294058252</v>
+        <v>0.131772729405825</v>
       </c>
       <c r="F23" t="n">
-        <v>4.278278685277821</v>
+        <v>4.278278685277815</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>512.6168055202986</v>
+        <v>512.6168055202979</v>
       </c>
       <c r="I23" t="n">
         <v>2980.877283748686</v>
       </c>
       <c r="J23" t="n">
-        <v>3.864156970198032</v>
+        <v>3.864156970198027</v>
       </c>
     </row>
     <row r="24">
@@ -1190,25 +1190,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1656348374493648</v>
+        <v>0.1656348374493649</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1270068206646132</v>
+        <v>0.1270068206646133</v>
       </c>
       <c r="F24" t="n">
-        <v>4.287945673533749</v>
+        <v>4.287945673533751</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>514.5086984406419</v>
+        <v>514.5086984406421</v>
       </c>
       <c r="I24" t="n">
         <v>3106.283112681106</v>
       </c>
       <c r="J24" t="n">
-        <v>3.729092756402992</v>
+        <v>3.729092756402999</v>
       </c>
     </row>
     <row r="25">
@@ -1228,19 +1228,19 @@
         <v>0.1287382332705082</v>
       </c>
       <c r="F25" t="n">
-        <v>4.457599970027378</v>
+        <v>4.457599970027377</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>535.5348976590852</v>
+        <v>535.5348976590851</v>
       </c>
       <c r="I25" t="n">
         <v>3226.665054744453</v>
       </c>
       <c r="J25" t="n">
-        <v>3.681753471465552</v>
+        <v>3.68175347146555</v>
       </c>
     </row>
     <row r="26">
@@ -1286,25 +1286,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1679189404399179</v>
+        <v>0.1679189404399183</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1338172576710621</v>
+        <v>0.1338172576710626</v>
       </c>
       <c r="F27" t="n">
-        <v>4.924066110698617</v>
+        <v>4.924066110698629</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>582.7173807094437</v>
+        <v>582.717380709445</v>
       </c>
       <c r="I27" t="n">
         <v>3470.23021454773</v>
       </c>
       <c r="J27" t="n">
-        <v>3.701626443334423</v>
+        <v>3.70162644333443</v>
       </c>
     </row>
     <row r="28">
@@ -1318,25 +1318,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1898143693767541</v>
+        <v>0.1898143693767539</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1576641459393237</v>
+        <v>0.1576641459393234</v>
       </c>
       <c r="F28" t="n">
-        <v>5.903982899097546</v>
+        <v>5.903982899097537</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>694.32797923934</v>
+        <v>694.3279792393391</v>
       </c>
       <c r="I28" t="n">
         <v>3657.931596639026</v>
       </c>
       <c r="J28" t="n">
-        <v>4.402790676006609</v>
+        <v>4.402790676006603</v>
       </c>
     </row>
     <row r="29">
@@ -1350,25 +1350,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1866738930901129</v>
+        <v>0.186673893090113</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1556309119103462</v>
+        <v>0.1556309119103463</v>
       </c>
       <c r="F29" t="n">
-        <v>6.013400968454149</v>
+        <v>6.013400968454151</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>703.1646919310973</v>
+        <v>703.1646919310977</v>
       </c>
       <c r="I29" t="n">
         <v>3766.807882405171</v>
       </c>
       <c r="J29" t="n">
-        <v>4.252153723259523</v>
+        <v>4.252153723259525</v>
       </c>
     </row>
     <row r="30">
@@ -1388,19 +1388,19 @@
         <v>0.1566704336469271</v>
       </c>
       <c r="F30" t="n">
-        <v>6.238884541839533</v>
+        <v>6.238884541839532</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>724.8835435249122</v>
+        <v>724.8835435249121</v>
       </c>
       <c r="I30" t="n">
         <v>3885.197258525015</v>
       </c>
       <c r="J30" t="n">
-        <v>4.240454106634709</v>
+        <v>4.240454106634712</v>
       </c>
     </row>
     <row r="31">
@@ -1414,25 +1414,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1843405653621117</v>
+        <v>0.1843405653621116</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1552098712679014</v>
+        <v>0.1552098712679011</v>
       </c>
       <c r="F31" t="n">
-        <v>6.328052629502888</v>
+        <v>6.328052629502882</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>735.4403061166397</v>
+        <v>735.440306116639</v>
       </c>
       <c r="I31" t="n">
         <v>3989.573888264735</v>
       </c>
       <c r="J31" t="n">
-        <v>4.12050358010924</v>
+        <v>4.120503580109239</v>
       </c>
     </row>
     <row r="32">
@@ -1446,25 +1446,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.196494151644095</v>
+        <v>0.1964941516440948</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1687870534249258</v>
+        <v>0.1687870534249256</v>
       </c>
       <c r="F32" t="n">
-        <v>7.091834377233721</v>
+        <v>7.091834377233714</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>826.9751029509093</v>
+        <v>826.9751029509085</v>
       </c>
       <c r="I32" t="n">
         <v>4208.649957423613</v>
       </c>
       <c r="J32" t="n">
-        <v>4.613896777623493</v>
+        <v>4.613896777623492</v>
       </c>
     </row>
     <row r="33">
@@ -1481,22 +1481,22 @@
         <v>0.1909420999615216</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1639735032935723</v>
+        <v>0.1639735032935722</v>
       </c>
       <c r="F33" t="n">
-        <v>7.08016447101402</v>
+        <v>7.080164471014019</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>829.6509627524454</v>
+        <v>829.6509627524451</v>
       </c>
       <c r="I33" t="n">
         <v>4345.039480133692</v>
       </c>
       <c r="J33" t="n">
-        <v>4.416299335543786</v>
+        <v>4.416299335543783</v>
       </c>
     </row>
     <row r="34">
@@ -1522,13 +1522,13 @@
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>830.7790011658839</v>
+        <v>830.779001165884</v>
       </c>
       <c r="I34" t="n">
         <v>4427.708897652928</v>
       </c>
       <c r="J34" t="n">
-        <v>4.367324964565433</v>
+        <v>4.367324964565431</v>
       </c>
     </row>
     <row r="35">
@@ -1542,25 +1542,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1912594112921341</v>
+        <v>0.191259411292134</v>
       </c>
       <c r="E35" t="n">
-        <v>0.16582731730761</v>
+        <v>0.1658273173076099</v>
       </c>
       <c r="F35" t="n">
-        <v>7.520395741244077</v>
+        <v>7.520395741244072</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>871.9509590643812</v>
+        <v>871.9509590643808</v>
       </c>
       <c r="I35" t="n">
         <v>4558.996355648836</v>
       </c>
       <c r="J35" t="n">
-        <v>4.470009394257569</v>
+        <v>4.470009394257567</v>
       </c>
     </row>
     <row r="36">
@@ -1574,25 +1574,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1977795627045712</v>
+        <v>0.1977795627045713</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1733216225431252</v>
+        <v>0.1733216225431253</v>
       </c>
       <c r="F36" t="n">
-        <v>8.086517564399752</v>
+        <v>8.086517564399758</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>928.9421551934223</v>
+        <v>928.9421551934228</v>
       </c>
       <c r="I36" t="n">
         <v>4696.856148787268</v>
       </c>
       <c r="J36" t="n">
-        <v>4.650872677087458</v>
+        <v>4.65087267708746</v>
       </c>
     </row>
     <row r="37">
@@ -1612,19 +1612,19 @@
         <v>0.1773327946567735</v>
       </c>
       <c r="F37" t="n">
-        <v>8.458319300043655</v>
+        <v>8.45831930004365</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>963.7787172298437</v>
+        <v>963.7787172298434</v>
       </c>
       <c r="I37" t="n">
         <v>4792.312939005513</v>
       </c>
       <c r="J37" t="n">
-        <v>4.745112312625918</v>
+        <v>4.745112312625917</v>
       </c>
     </row>
     <row r="38">
@@ -1638,25 +1638,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1967908023501506</v>
+        <v>0.1967908023501508</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1735766636897502</v>
+        <v>0.1735766636897504</v>
       </c>
       <c r="F38" t="n">
-        <v>8.477195954973997</v>
+        <v>8.477195954974007</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>967.3026022796006</v>
+        <v>967.3026022796018</v>
       </c>
       <c r="I38" t="n">
         <v>4915.385224958205</v>
       </c>
       <c r="J38" t="n">
-        <v>4.622249544946809</v>
+        <v>4.622249544946817</v>
       </c>
     </row>
     <row r="39">
@@ -1670,25 +1670,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1998056512523499</v>
+        <v>0.1998056512523497</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1773282819055059</v>
+        <v>0.1773282819055056</v>
       </c>
       <c r="F39" t="n">
-        <v>8.889191976569238</v>
+        <v>8.889191976569229</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>1003.08029839762</v>
+        <v>1003.080298397619</v>
       </c>
       <c r="I39" t="n">
         <v>5020.279917562256</v>
       </c>
       <c r="J39" t="n">
-        <v>4.709001941985301</v>
+        <v>4.709001941985292</v>
       </c>
     </row>
     <row r="40">
@@ -1702,25 +1702,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2003347081567013</v>
+        <v>0.2003347081567015</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1783658814577096</v>
+        <v>0.1783658814577099</v>
       </c>
       <c r="F40" t="n">
-        <v>9.11904449434688</v>
+        <v>9.119044494346888</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>1016.21423105763</v>
+        <v>1016.214231057631</v>
       </c>
       <c r="I40" t="n">
         <v>5072.581982462818</v>
       </c>
       <c r="J40" t="n">
-        <v>4.674361523025206</v>
+        <v>4.67436152302521</v>
       </c>
     </row>
     <row r="41">
@@ -1734,25 +1734,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2004832439013848</v>
+        <v>0.2004832439013847</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1791057905297641</v>
+        <v>0.1791057905297638</v>
       </c>
       <c r="F41" t="n">
-        <v>9.378256634044767</v>
+        <v>9.378256634044764</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>1035.149830666143</v>
+        <v>1035.149830666142</v>
       </c>
       <c r="I41" t="n">
         <v>5163.273551057066</v>
       </c>
       <c r="J41" t="n">
-        <v>4.631984768158491</v>
+        <v>4.631984768158489</v>
       </c>
     </row>
     <row r="42">
@@ -1766,25 +1766,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1966770500476557</v>
+        <v>0.196677050047656</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1757571815593134</v>
+        <v>0.1757571815593136</v>
       </c>
       <c r="F42" t="n">
-        <v>9.401447726942214</v>
+        <v>9.401447726942227</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>1044.160908794896</v>
+        <v>1044.160908794897</v>
       </c>
       <c r="I42" t="n">
         <v>5309.012457436651</v>
       </c>
       <c r="J42" t="n">
-        <v>4.565004657665559</v>
+        <v>4.565004657665564</v>
       </c>
     </row>
     <row r="43">
@@ -1798,25 +1798,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1910186752401951</v>
+        <v>0.1910186752401954</v>
       </c>
       <c r="E43" t="n">
-        <v>0.170381396547343</v>
+        <v>0.1703813965473432</v>
       </c>
       <c r="F43" t="n">
-        <v>9.256001146428064</v>
+        <v>9.256001146428074</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>1033.546991268666</v>
+        <v>1033.546991268668</v>
       </c>
       <c r="I43" t="n">
         <v>5410.711753544724</v>
       </c>
       <c r="J43" t="n">
-        <v>4.412718370940306</v>
+        <v>4.412718370940309</v>
       </c>
     </row>
     <row r="44">
@@ -1830,25 +1830,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.189965134535225</v>
+        <v>0.1899651345352254</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1698150135037628</v>
+        <v>0.1698150135037633</v>
       </c>
       <c r="F44" t="n">
-        <v>9.427493474536282</v>
+        <v>9.427493474536309</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1060.365810237204</v>
+        <v>1060.365810237207</v>
       </c>
       <c r="I44" t="n">
         <v>5581.896977208637</v>
       </c>
       <c r="J44" t="n">
-        <v>4.482980887075852</v>
+        <v>4.482980887075862</v>
       </c>
     </row>
     <row r="45">
@@ -1862,25 +1862,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1944542017511583</v>
+        <v>0.194454201751158</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1749021192693904</v>
+        <v>0.17490211926939</v>
       </c>
       <c r="F45" t="n">
-        <v>9.945447086390086</v>
+        <v>9.945447086390073</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1109.347921704105</v>
+        <v>1109.347921704103</v>
       </c>
       <c r="I45" t="n">
         <v>5704.931607102682</v>
       </c>
       <c r="J45" t="n">
-        <v>4.60419777221746</v>
+        <v>4.604197772217451</v>
       </c>
     </row>
     <row r="46">
@@ -1894,25 +1894,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1870785774178997</v>
+        <v>0.1870785774179001</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1677233054516593</v>
+        <v>0.1677233054516597</v>
       </c>
       <c r="F46" t="n">
-        <v>9.665510138230179</v>
+        <v>9.6655101382302</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1075.328205134727</v>
+        <v>1075.32820513473</v>
       </c>
       <c r="I46" t="n">
         <v>5748.002897908714</v>
       </c>
       <c r="J46" t="n">
-        <v>4.388162878357392</v>
+        <v>4.388162878357402</v>
       </c>
     </row>
     <row r="47">
@@ -1926,13 +1926,13 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1874142986462785</v>
+        <v>0.1874142986462784</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1685169567543314</v>
+        <v>0.1685169567543313</v>
       </c>
       <c r="F47" t="n">
-        <v>9.917495260333091</v>
+        <v>9.917495260333087</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
@@ -1944,7 +1944,7 @@
         <v>5864.345167020192</v>
       </c>
       <c r="J47" t="n">
-        <v>4.402013526601421</v>
+        <v>4.402013526601426</v>
       </c>
     </row>
     <row r="48">
@@ -1958,25 +1958,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1854214466450856</v>
+        <v>0.1854214466450859</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1669082977052011</v>
+        <v>0.1669082977052015</v>
       </c>
       <c r="F48" t="n">
-        <v>10.01566223267489</v>
+        <v>10.01566223267491</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1103.682521513987</v>
+        <v>1103.682521513989</v>
       </c>
       <c r="I48" t="n">
         <v>5952.291611803357</v>
       </c>
       <c r="J48" t="n">
-        <v>4.298214931583267</v>
+        <v>4.298214931583275</v>
       </c>
     </row>
     <row r="49">
@@ -1996,7 +1996,7 @@
         <v>0.1676857096888021</v>
       </c>
       <c r="F49" t="n">
-        <v>10.34817174249319</v>
+        <v>10.3481717424932</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
@@ -2008,7 +2008,7 @@
         <v>6120.49474534301</v>
       </c>
       <c r="J49" t="n">
-        <v>4.30934533691014</v>
+        <v>4.309345336910141</v>
       </c>
     </row>
   </sheetData>

--- a/results/ref_threshold_sensitivity/tables/MaxRel_threshold_metrics.xlsx
+++ b/results/ref_threshold_sensitivity/tables/MaxRel_threshold_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,25 +486,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4540647766946753</v>
+        <v>0.5042739129028468</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.09187044661064947</v>
+        <v>0.008547825805693687</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8317191441606815</v>
+        <v>1.017243042131891</v>
       </c>
       <c r="G2" t="n">
-        <v>0.663</v>
+        <v>0.471</v>
       </c>
       <c r="H2" t="n">
-        <v>155.8593159772076</v>
+        <v>101.4748901356991</v>
       </c>
       <c r="I2" t="n">
-        <v>343.25348271181</v>
+        <v>201.2297038162456</v>
       </c>
       <c r="J2" t="n">
-        <v>9.152322810631675</v>
+        <v>3.902968091160643</v>
       </c>
     </row>
     <row r="3">
@@ -518,25 +518,25 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.337553379043599</v>
+        <v>0.2966481564618892</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006330068565398417</v>
+        <v>-0.05502776530716602</v>
       </c>
       <c r="F3" t="n">
-        <v>1.019111180780905</v>
+        <v>0.8435270602822149</v>
       </c>
       <c r="G3" t="n">
-        <v>0.448</v>
+        <v>0.662</v>
       </c>
       <c r="H3" t="n">
-        <v>149.7692047607856</v>
+        <v>91.23315384950106</v>
       </c>
       <c r="I3" t="n">
-        <v>443.6904325624929</v>
+        <v>307.5466739373514</v>
       </c>
       <c r="J3" t="n">
-        <v>6.19078208535838</v>
+        <v>3.080494560550398</v>
       </c>
     </row>
     <row r="4">
@@ -550,25 +550,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2690628190827337</v>
+        <v>0.2654594980853385</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008013825897995597</v>
+        <v>0.003123604544387981</v>
       </c>
       <c r="F4" t="n">
-        <v>1.030698551257481</v>
+        <v>1.011906889683399</v>
       </c>
       <c r="G4" t="n">
-        <v>0.45</v>
+        <v>0.479</v>
       </c>
       <c r="H4" t="n">
-        <v>148.9924651300705</v>
+        <v>102.6262459548834</v>
       </c>
       <c r="I4" t="n">
-        <v>553.7460197510866</v>
+        <v>386.5985082285195</v>
       </c>
       <c r="J4" t="n">
-        <v>4.669555028397697</v>
+        <v>2.10644476558896</v>
       </c>
     </row>
     <row r="5">
@@ -582,25 +582,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2490882289063756</v>
+        <v>0.2609479173050455</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05147986809226401</v>
+        <v>0.06646052712216277</v>
       </c>
       <c r="F5" t="n">
-        <v>1.260514625394269</v>
+        <v>1.341721522715009</v>
       </c>
       <c r="G5" t="n">
-        <v>0.173</v>
+        <v>0.152</v>
       </c>
       <c r="H5" t="n">
-        <v>177.0048403230225</v>
+        <v>121.4872235431336</v>
       </c>
       <c r="I5" t="n">
-        <v>710.6110196381584</v>
+        <v>465.5611924318072</v>
       </c>
       <c r="J5" t="n">
-        <v>3.981816140151957</v>
+        <v>2.423228082882431</v>
       </c>
     </row>
     <row r="6">
@@ -614,25 +614,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2290282931613529</v>
+        <v>0.1818257080951598</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06840918756996806</v>
+        <v>0.01137273061498478</v>
       </c>
       <c r="F6" t="n">
-        <v>1.425909404227422</v>
+        <v>1.066720633356537</v>
       </c>
       <c r="G6" t="n">
-        <v>0.082</v>
+        <v>0.398</v>
       </c>
       <c r="H6" t="n">
-        <v>187.9845131799059</v>
+        <v>101.0275905128577</v>
       </c>
       <c r="I6" t="n">
-        <v>820.7916610873438</v>
+        <v>555.628747833525</v>
       </c>
       <c r="J6" t="n">
-        <v>3.660958835599077</v>
+        <v>1.390357751478525</v>
       </c>
     </row>
     <row r="7">
@@ -646,25 +646,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2256937344639147</v>
+        <v>0.1676593553039323</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08742475847532805</v>
+        <v>0.01902709732249164</v>
       </c>
       <c r="F7" t="n">
-        <v>1.63228036405321</v>
+        <v>1.128014588359867</v>
       </c>
       <c r="G7" t="n">
-        <v>0.027</v>
+        <v>0.277</v>
       </c>
       <c r="H7" t="n">
-        <v>199.8354509940641</v>
+        <v>108.1603690918435</v>
       </c>
       <c r="I7" t="n">
-        <v>885.4275528238688</v>
+        <v>645.1197960040508</v>
       </c>
       <c r="J7" t="n">
-        <v>3.447740269724831</v>
+        <v>1.322822848148824</v>
       </c>
     </row>
     <row r="8">
@@ -678,25 +678,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2041629597528989</v>
+        <v>0.1469969673256371</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08358159001848953</v>
+        <v>0.01775408358709718</v>
       </c>
       <c r="F8" t="n">
-        <v>1.693155088572847</v>
+        <v>1.137369912164867</v>
       </c>
       <c r="G8" t="n">
-        <v>0.026</v>
+        <v>0.281</v>
       </c>
       <c r="H8" t="n">
-        <v>194.4687604532768</v>
+        <v>115.7263833573242</v>
       </c>
       <c r="I8" t="n">
-        <v>952.5173454021478</v>
+        <v>787.2705502893788</v>
       </c>
       <c r="J8" t="n">
-        <v>3.037457404256481</v>
+        <v>1.275245289219449</v>
       </c>
     </row>
     <row r="9">
@@ -710,25 +710,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2171090769975938</v>
+        <v>0.1687476343566744</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1140971134446457</v>
+        <v>0.05937232308781581</v>
       </c>
       <c r="F9" t="n">
-        <v>2.107610315436806</v>
+        <v>1.54283112339558</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005</v>
+        <v>0.044</v>
       </c>
       <c r="H9" t="n">
-        <v>237.7647795625752</v>
+        <v>152.4526113317228</v>
       </c>
       <c r="I9" t="n">
-        <v>1095.139746576373</v>
+        <v>903.4355468918189</v>
       </c>
       <c r="J9" t="n">
-        <v>3.535853256994268</v>
+        <v>1.782592630980634</v>
       </c>
     </row>
     <row r="10">
@@ -742,25 +742,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2164837485069393</v>
+        <v>0.149108946425533</v>
       </c>
       <c r="E10" t="n">
-        <v>0.123208004281575</v>
+        <v>0.0478123924285726</v>
       </c>
       <c r="F10" t="n">
-        <v>2.320900790498021</v>
+        <v>1.472004135797229</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002</v>
+        <v>0.034</v>
       </c>
       <c r="H10" t="n">
-        <v>265.813545913641</v>
+        <v>150.7256656452056</v>
       </c>
       <c r="I10" t="n">
-        <v>1227.868363084633</v>
+        <v>1010.842536671534</v>
       </c>
       <c r="J10" t="n">
-        <v>3.467782559166384</v>
+        <v>1.562596092827975</v>
       </c>
     </row>
     <row r="11">
@@ -774,25 +774,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2491154112060493</v>
+        <v>0.1482641801720487</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1692340719726503</v>
+        <v>0.05765398657333054</v>
       </c>
       <c r="F11" t="n">
-        <v>3.118568286370094</v>
+        <v>1.636285877819227</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001</v>
+        <v>0.017</v>
       </c>
       <c r="H11" t="n">
-        <v>355.863744313806</v>
+        <v>159.3291901584869</v>
       </c>
       <c r="I11" t="n">
-        <v>1428.509551420176</v>
+        <v>1074.630365699916</v>
       </c>
       <c r="J11" t="n">
-        <v>4.898928794356264</v>
+        <v>1.596867729615576</v>
       </c>
     </row>
     <row r="12">
@@ -806,25 +806,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2611641873873121</v>
+        <v>0.1345602321711464</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1901222823283997</v>
+        <v>0.05134486987991038</v>
       </c>
       <c r="F12" t="n">
-        <v>3.676199099260341</v>
+        <v>1.617011913019311</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="H12" t="n">
-        <v>414.5751402959819</v>
+        <v>152.8027835636105</v>
       </c>
       <c r="I12" t="n">
-        <v>1587.411905297559</v>
+        <v>1135.571640284192</v>
       </c>
       <c r="J12" t="n">
-        <v>5.421913695254558</v>
+        <v>1.424204211940749</v>
       </c>
     </row>
     <row r="13">
@@ -838,25 +838,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2596740034226862</v>
+        <v>0.1401088636947223</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1935734680139976</v>
+        <v>0.0633328693817512</v>
       </c>
       <c r="F13" t="n">
-        <v>3.928470500536262</v>
+        <v>1.824904580507023</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H13" t="n">
-        <v>450.9244023184474</v>
+        <v>179.5144878225149</v>
       </c>
       <c r="I13" t="n">
-        <v>1736.501907680192</v>
+        <v>1281.250044348742</v>
       </c>
       <c r="J13" t="n">
-        <v>5.542146240870014</v>
+        <v>1.495862608029784</v>
       </c>
     </row>
     <row r="14">
@@ -870,25 +870,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2286852390593461</v>
+        <v>0.1506097352590443</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1654627176707678</v>
+        <v>0.0809875824114249</v>
       </c>
       <c r="F14" t="n">
-        <v>3.617148352148141</v>
+        <v>2.163244443024923</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H14" t="n">
-        <v>423.7689487047983</v>
+        <v>223.1196706475193</v>
       </c>
       <c r="I14" t="n">
-        <v>1853.066470087412</v>
+        <v>1481.442552593031</v>
       </c>
       <c r="J14" t="n">
-        <v>4.831600427020523</v>
+        <v>2.24090961559351</v>
       </c>
     </row>
     <row r="15">
@@ -902,25 +902,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2007699431303815</v>
+        <v>0.1677506624327929</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1402222115493499</v>
+        <v>0.104701470192853</v>
       </c>
       <c r="F15" t="n">
-        <v>3.315895375232826</v>
+        <v>2.660631428780263</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>400.7771584283195</v>
+        <v>276.3840127261318</v>
       </c>
       <c r="I15" t="n">
-        <v>1996.200985961587</v>
+        <v>1647.58820452862</v>
       </c>
       <c r="J15" t="n">
-        <v>4.300665574403083</v>
+        <v>2.767721545806567</v>
       </c>
     </row>
     <row r="16">
@@ -934,25 +934,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2008168961751941</v>
+        <v>0.1645950767537591</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1437323887591366</v>
+        <v>0.1049232965218847</v>
       </c>
       <c r="F16" t="n">
-        <v>3.51788786949759</v>
+        <v>2.758340309509298</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>429.6952753753981</v>
+        <v>284.0333743226835</v>
       </c>
       <c r="I16" t="n">
-        <v>2139.736663395737</v>
+        <v>1725.649271682706</v>
       </c>
       <c r="J16" t="n">
-        <v>4.405752670014369</v>
+        <v>2.687765153834455</v>
       </c>
     </row>
     <row r="17">
@@ -966,25 +966,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.179415035002062</v>
+        <v>0.1794556844377696</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1247093706688661</v>
+        <v>0.1247527300669543</v>
       </c>
       <c r="F17" t="n">
-        <v>3.279642742464448</v>
+        <v>3.280548308621358</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>407.3769694764215</v>
+        <v>340.421121789901</v>
       </c>
       <c r="I17" t="n">
-        <v>2270.584343568194</v>
+        <v>1896.964829263738</v>
       </c>
       <c r="J17" t="n">
-        <v>3.907193209204044</v>
+        <v>3.237074549161874</v>
       </c>
     </row>
     <row r="18">
@@ -998,25 +998,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1779500355663928</v>
+        <v>0.1649553184404655</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1265719127892924</v>
+        <v>0.1127650258429946</v>
       </c>
       <c r="F18" t="n">
-        <v>3.463537123347494</v>
+        <v>3.160651343971564</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>423.0218300961284</v>
+        <v>333.579261550729</v>
       </c>
       <c r="I18" t="n">
-        <v>2377.19441162067</v>
+        <v>2022.240111470683</v>
       </c>
       <c r="J18" t="n">
-        <v>3.875880155216719</v>
+        <v>2.9347424021878</v>
       </c>
     </row>
     <row r="19">
@@ -1030,25 +1030,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1801093091118439</v>
+        <v>0.1560905414672123</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1313062917970728</v>
+        <v>0.1058578356021653</v>
       </c>
       <c r="F19" t="n">
-        <v>3.690536344303659</v>
+        <v>3.107348863239793</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>444.3413602864088</v>
+        <v>329.4498598879989</v>
       </c>
       <c r="I19" t="n">
-        <v>2467.064931166232</v>
+        <v>2110.633077387342</v>
       </c>
       <c r="J19" t="n">
-        <v>3.990592698089626</v>
+        <v>2.763214469745415</v>
       </c>
     </row>
     <row r="20">
@@ -1062,25 +1062,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1812893623035288</v>
+        <v>0.1566144224839928</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1352943826576597</v>
+        <v>0.1092332102639925</v>
       </c>
       <c r="F20" t="n">
-        <v>3.941503261863284</v>
+        <v>3.305411895263482</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>471.4850423811632</v>
+        <v>355.0120681327314</v>
       </c>
       <c r="I20" t="n">
-        <v>2600.731981128414</v>
+        <v>2266.790391983321</v>
       </c>
       <c r="J20" t="n">
-        <v>4.092750561468098</v>
+        <v>2.833357405306586</v>
       </c>
     </row>
     <row r="21">
@@ -1094,25 +1094,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1748967880624035</v>
+        <v>0.1546395804306359</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1310083193423186</v>
+        <v>0.1096736006663082</v>
       </c>
       <c r="F21" t="n">
-        <v>3.985028258285178</v>
+        <v>3.439035049188756</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>482.4602509001276</v>
+        <v>359.9370935525363</v>
       </c>
       <c r="I21" t="n">
-        <v>2758.542659616967</v>
+        <v>2327.587106419932</v>
       </c>
       <c r="J21" t="n">
-        <v>3.915466250254436</v>
+        <v>2.746880925123897</v>
       </c>
     </row>
     <row r="22">
@@ -1126,25 +1126,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1693897411386435</v>
+        <v>0.1497828348854159</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1270116667069416</v>
+        <v>0.1064044080938555</v>
       </c>
       <c r="F22" t="n">
-        <v>3.99710801895066</v>
+        <v>3.452933772936118</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>480.3095104593779</v>
+        <v>364.4547814147135</v>
       </c>
       <c r="I22" t="n">
-        <v>2835.528924188215</v>
+        <v>2433.221281287152</v>
       </c>
       <c r="J22" t="n">
-        <v>3.734636310543169</v>
+        <v>2.748546050348216</v>
       </c>
     </row>
     <row r="23">
@@ -1158,25 +1158,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1719684363777775</v>
+        <v>0.1448825951666754</v>
       </c>
       <c r="E23" t="n">
-        <v>0.131772729405825</v>
+        <v>0.1033720415339898</v>
       </c>
       <c r="F23" t="n">
-        <v>4.278278685277815</v>
+        <v>3.490259283186095</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>512.6168055202979</v>
+        <v>368.9325122374968</v>
       </c>
       <c r="I23" t="n">
-        <v>2980.877283748686</v>
+        <v>2546.42396357596</v>
       </c>
       <c r="J23" t="n">
-        <v>3.864156970198027</v>
+        <v>2.604856506828096</v>
       </c>
     </row>
     <row r="24">
@@ -1190,25 +1190,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1656348374493649</v>
+        <v>0.1419337867009056</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1270068206646133</v>
+        <v>0.1022084990481698</v>
       </c>
       <c r="F24" t="n">
-        <v>4.287945673533751</v>
+        <v>3.572882541257841</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>514.5086984406421</v>
+        <v>379.2516364397864</v>
       </c>
       <c r="I24" t="n">
-        <v>3106.283112681106</v>
+        <v>2672.032116207653</v>
       </c>
       <c r="J24" t="n">
-        <v>3.729092756402999</v>
+        <v>2.550314473249522</v>
       </c>
     </row>
     <row r="25">
@@ -1222,25 +1222,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1659716421051018</v>
+        <v>0.151262013971253</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1287382332705082</v>
+        <v>0.1133719253092553</v>
       </c>
       <c r="F25" t="n">
-        <v>4.457599970027377</v>
+        <v>3.992126155222307</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>535.5348976590851</v>
+        <v>429.2740675048523</v>
       </c>
       <c r="I25" t="n">
-        <v>3226.665054744453</v>
+        <v>2837.950231089974</v>
       </c>
       <c r="J25" t="n">
-        <v>3.68175347146555</v>
+        <v>2.900720690521111</v>
       </c>
     </row>
     <row r="26">
@@ -1254,25 +1254,25 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1708156489504472</v>
+        <v>0.1465969415152222</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1353804202731158</v>
+        <v>0.1101267253406589</v>
       </c>
       <c r="F26" t="n">
-        <v>4.820503643587934</v>
+        <v>4.019634564641517</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>574.8974300223044</v>
+        <v>441.8323448208064</v>
       </c>
       <c r="I26" t="n">
-        <v>3365.601650403116</v>
+        <v>3013.926076861077</v>
       </c>
       <c r="J26" t="n">
-        <v>3.825871802688662</v>
+        <v>2.896854663869406</v>
       </c>
     </row>
     <row r="27">
@@ -1286,25 +1286,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1679189404399183</v>
+        <v>0.1407894527660243</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1338172576710626</v>
+        <v>0.1055759057482385</v>
       </c>
       <c r="F27" t="n">
-        <v>4.924066110698629</v>
+        <v>3.998161636341644</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>582.717380709445</v>
+        <v>440.9339315218399</v>
       </c>
       <c r="I27" t="n">
-        <v>3470.23021454773</v>
+        <v>3131.867642490386</v>
       </c>
       <c r="J27" t="n">
-        <v>3.70162644333443</v>
+        <v>2.698532081920324</v>
       </c>
     </row>
     <row r="28">
@@ -1318,25 +1318,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1898143693767539</v>
+        <v>0.1528967118169647</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1576641459393234</v>
+        <v>0.1192815019684315</v>
       </c>
       <c r="F28" t="n">
-        <v>5.903982899097537</v>
+        <v>4.548438415404879</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>694.3279792393391</v>
+        <v>502.1719623564679</v>
       </c>
       <c r="I28" t="n">
-        <v>3657.931596639026</v>
+        <v>3284.386932778691</v>
       </c>
       <c r="J28" t="n">
-        <v>4.402790676006603</v>
+        <v>3.114672593397253</v>
       </c>
     </row>
     <row r="29">
@@ -1350,25 +1350,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.186673893090113</v>
+        <v>0.1490845495695475</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1556309119103463</v>
+        <v>0.1166068606218204</v>
       </c>
       <c r="F29" t="n">
-        <v>6.013400968454151</v>
+        <v>4.590368169653294</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>703.1646919310977</v>
+        <v>520.5474031994795</v>
       </c>
       <c r="I29" t="n">
-        <v>3766.807882405171</v>
+        <v>3491.625421295891</v>
       </c>
       <c r="J29" t="n">
-        <v>4.252153723259525</v>
+        <v>3.129747838091092</v>
       </c>
     </row>
     <row r="30">
@@ -1382,25 +1382,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1865757374183128</v>
+        <v>0.1534325856987356</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1566704336469271</v>
+        <v>0.1223087837023655</v>
       </c>
       <c r="F30" t="n">
-        <v>6.238884541839532</v>
+        <v>4.929750732787415</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>724.8835435249121</v>
+        <v>562.3563246871383</v>
       </c>
       <c r="I30" t="n">
-        <v>3885.197258525015</v>
+        <v>3665.168791402129</v>
       </c>
       <c r="J30" t="n">
-        <v>4.240454106634712</v>
+        <v>3.321285742448989</v>
       </c>
     </row>
     <row r="31">
@@ -1414,25 +1414,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1843405653621116</v>
+        <v>0.168289345053309</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1552098712679011</v>
+        <v>0.1385853930909271</v>
       </c>
       <c r="F31" t="n">
-        <v>6.328052629502882</v>
+        <v>5.665554040298638</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>735.440306116639</v>
+        <v>644.7108122577132</v>
       </c>
       <c r="I31" t="n">
-        <v>3989.573888264735</v>
+        <v>3830.966316099741</v>
       </c>
       <c r="J31" t="n">
-        <v>4.120503580109239</v>
+        <v>3.823402579158988</v>
       </c>
     </row>
     <row r="32">
@@ -1446,25 +1446,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1964941516440948</v>
+        <v>0.1720850554985721</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1687870534249256</v>
+        <v>0.1435362643088677</v>
       </c>
       <c r="F32" t="n">
-        <v>7.091834377233714</v>
+        <v>6.027752781372806</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>826.9751029509085</v>
+        <v>676.6237886045799</v>
       </c>
       <c r="I32" t="n">
-        <v>4208.649957423613</v>
+        <v>3931.914869912653</v>
       </c>
       <c r="J32" t="n">
-        <v>4.613896777623492</v>
+        <v>3.91224355456934</v>
       </c>
     </row>
     <row r="33">
@@ -1478,25 +1478,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1909420999615216</v>
+        <v>0.1747846511964646</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1639735032935722</v>
+        <v>0.1472774729030133</v>
       </c>
       <c r="F33" t="n">
-        <v>7.080164471014019</v>
+        <v>6.354146882382218</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>829.6509627524451</v>
+        <v>712.21156367652</v>
       </c>
       <c r="I33" t="n">
-        <v>4345.039480133692</v>
+        <v>4074.794661894924</v>
       </c>
       <c r="J33" t="n">
-        <v>4.416299335543783</v>
+        <v>3.979174807429905</v>
       </c>
     </row>
     <row r="34">
@@ -1510,25 +1510,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1876318024444356</v>
+        <v>0.1821908268148074</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1612562116147094</v>
+        <v>0.1556385809321712</v>
       </c>
       <c r="F34" t="n">
-        <v>7.113842630321995</v>
+        <v>6.861597607227316</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>830.779001165884</v>
+        <v>769.2567972180793</v>
       </c>
       <c r="I34" t="n">
-        <v>4427.708897652928</v>
+        <v>4222.258665086418</v>
       </c>
       <c r="J34" t="n">
-        <v>4.367324964565431</v>
+        <v>4.222662205621352</v>
       </c>
     </row>
     <row r="35">
@@ -1542,25 +1542,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.191259411292134</v>
+        <v>0.1888343459229176</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1658273173076099</v>
+        <v>0.1633259920211225</v>
       </c>
       <c r="F35" t="n">
-        <v>7.520395741244072</v>
+        <v>7.402843266559401</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>871.9509590643808</v>
+        <v>825.8447266220609</v>
       </c>
       <c r="I35" t="n">
-        <v>4558.996355648836</v>
+        <v>4373.381985071569</v>
       </c>
       <c r="J35" t="n">
-        <v>4.470009394257567</v>
+        <v>4.39233685854913</v>
       </c>
     </row>
     <row r="36">
@@ -1574,25 +1574,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1977795627045713</v>
+        <v>0.2012078875131355</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1733216225431253</v>
+        <v>0.1768544694495117</v>
       </c>
       <c r="F36" t="n">
-        <v>8.086517564399758</v>
+        <v>8.261997843073807</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>928.9421551934228</v>
+        <v>914.3137022691628</v>
       </c>
       <c r="I36" t="n">
-        <v>4696.856148787268</v>
+        <v>4544.124554806399</v>
       </c>
       <c r="J36" t="n">
-        <v>4.65087267708746</v>
+        <v>4.729378160306549</v>
       </c>
     </row>
     <row r="37">
@@ -1606,25 +1606,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2011093034817222</v>
+        <v>0.2055010768299387</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1773327946567735</v>
+        <v>0.1818552755451155</v>
       </c>
       <c r="F37" t="n">
-        <v>8.45831930004365</v>
+        <v>8.690806217754899</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>963.7787172298434</v>
+        <v>961.142951123591</v>
       </c>
       <c r="I37" t="n">
-        <v>4792.312939005513</v>
+        <v>4677.070144595786</v>
       </c>
       <c r="J37" t="n">
-        <v>4.745112312625917</v>
+        <v>4.908722815592427</v>
       </c>
     </row>
     <row r="38">
@@ -1638,25 +1638,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1967908023501508</v>
+        <v>0.1987714370095047</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1735766636897504</v>
+        <v>0.1756145421253863</v>
       </c>
       <c r="F38" t="n">
-        <v>8.477195954974007</v>
+        <v>8.583682657117713</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>967.3026022796018</v>
+        <v>943.4880887690178</v>
       </c>
       <c r="I38" t="n">
-        <v>4915.385224958205</v>
+        <v>4746.597916499959</v>
       </c>
       <c r="J38" t="n">
-        <v>4.622249544946817</v>
+        <v>4.663668706038773</v>
       </c>
     </row>
     <row r="39">
@@ -1670,25 +1670,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1998056512523497</v>
+        <v>0.1967275407975825</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1773282819055056</v>
+        <v>0.1741637076739191</v>
       </c>
       <c r="F39" t="n">
-        <v>8.889191976569229</v>
+        <v>8.718711032801785</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>1003.080298397619</v>
+        <v>967.1574683655841</v>
       </c>
       <c r="I39" t="n">
-        <v>5020.279917562256</v>
+        <v>4916.228121616763</v>
       </c>
       <c r="J39" t="n">
-        <v>4.709001941985292</v>
+        <v>4.65635620396491</v>
       </c>
     </row>
     <row r="40">
@@ -1702,25 +1702,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2003347081567015</v>
+        <v>0.1955789478378163</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1783658814577099</v>
+        <v>0.1734794683828113</v>
       </c>
       <c r="F40" t="n">
-        <v>9.119044494346888</v>
+        <v>8.849934598505756</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>1016.214231057631</v>
+        <v>976.0468205389818</v>
       </c>
       <c r="I40" t="n">
-        <v>5072.581982462818</v>
+        <v>4990.551546214308</v>
       </c>
       <c r="J40" t="n">
-        <v>4.67436152302521</v>
+        <v>4.587497888307963</v>
       </c>
     </row>
     <row r="41">
@@ -1734,25 +1734,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2004832439013847</v>
+        <v>0.1967642950820772</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1791057905297638</v>
+        <v>0.1752874045762502</v>
       </c>
       <c r="F41" t="n">
-        <v>9.378256634044764</v>
+        <v>9.161675198217997</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>1035.149830666142</v>
+        <v>1001.300554850719</v>
       </c>
       <c r="I41" t="n">
-        <v>5163.273551057066</v>
+        <v>5088.832577236851</v>
       </c>
       <c r="J41" t="n">
-        <v>4.631984768158489</v>
+        <v>4.585869505958987</v>
       </c>
     </row>
     <row r="42">
@@ -1766,25 +1766,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.196677050047656</v>
+        <v>0.1939583217957061</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1757571815593136</v>
+        <v>0.1729676530924693</v>
       </c>
       <c r="F42" t="n">
-        <v>9.401447726942227</v>
+        <v>9.240216428445523</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>1044.160908794897</v>
+        <v>1010.244210606835</v>
       </c>
       <c r="I42" t="n">
-        <v>5309.012457436651</v>
+        <v>5208.563372036764</v>
       </c>
       <c r="J42" t="n">
-        <v>4.565004657665564</v>
+        <v>4.512554784940402</v>
       </c>
     </row>
     <row r="43">
@@ -1798,25 +1798,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1910186752401954</v>
+        <v>0.1928465981161138</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1703813965473432</v>
+        <v>0.1722559501088718</v>
       </c>
       <c r="F43" t="n">
-        <v>9.256001146428074</v>
+        <v>9.365737204981947</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>1033.546991268668</v>
+        <v>1020.81860204309</v>
       </c>
       <c r="I43" t="n">
-        <v>5410.711753544724</v>
+        <v>5293.42291756918</v>
       </c>
       <c r="J43" t="n">
-        <v>4.412718370940309</v>
+        <v>4.459532457984951</v>
       </c>
     </row>
     <row r="44">
@@ -1830,25 +1830,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1899651345352254</v>
+        <v>0.19341272527449</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1698150135037633</v>
+        <v>0.1733483652066912</v>
       </c>
       <c r="F44" t="n">
-        <v>9.427493474536309</v>
+        <v>9.639615946929583</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1060.365810237207</v>
+        <v>1040.384165363156</v>
       </c>
       <c r="I44" t="n">
-        <v>5581.896977208637</v>
+        <v>5379.088495271708</v>
       </c>
       <c r="J44" t="n">
-        <v>4.482980887075862</v>
+        <v>4.439575338383418</v>
       </c>
     </row>
     <row r="45">
@@ -1862,25 +1862,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.194454201751158</v>
+        <v>0.1954239880917322</v>
       </c>
       <c r="E45" t="n">
-        <v>0.17490211926939</v>
+        <v>0.1758954441133761</v>
       </c>
       <c r="F45" t="n">
-        <v>9.945447086390073</v>
+        <v>10.00709465633104</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1109.347921704103</v>
+        <v>1087.619663043725</v>
       </c>
       <c r="I45" t="n">
-        <v>5704.931607102682</v>
+        <v>5565.435818110494</v>
       </c>
       <c r="J45" t="n">
-        <v>4.604197772217451</v>
+        <v>4.551947875484112</v>
       </c>
     </row>
     <row r="46">
@@ -1894,25 +1894,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1870785774179001</v>
+        <v>0.1904827117315498</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1677233054516597</v>
+        <v>0.171208490582301</v>
       </c>
       <c r="F46" t="n">
-        <v>9.6655101382302</v>
+        <v>9.882770891573673</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1075.32820513473</v>
+        <v>1084.589043483569</v>
       </c>
       <c r="I46" t="n">
-        <v>5748.002897908714</v>
+        <v>5693.897538649579</v>
       </c>
       <c r="J46" t="n">
-        <v>4.388162878357402</v>
+        <v>4.471647866738395</v>
       </c>
     </row>
     <row r="47">
@@ -1926,25 +1926,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1874142986462784</v>
+        <v>0.1884090460244263</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1685169567543313</v>
+        <v>0.1695348377924362</v>
       </c>
       <c r="F47" t="n">
-        <v>9.917495260333087</v>
+        <v>9.982354952781003</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1099.062136496782</v>
+        <v>1091.249558821619</v>
       </c>
       <c r="I47" t="n">
-        <v>5864.345167020192</v>
+        <v>5791.917011671213</v>
       </c>
       <c r="J47" t="n">
-        <v>4.402013526601426</v>
+        <v>4.394807317206665</v>
       </c>
     </row>
     <row r="48">
@@ -1958,25 +1958,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1854214466450859</v>
+        <v>0.1823331736476731</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1669082977052015</v>
+        <v>0.1637498366851202</v>
       </c>
       <c r="F48" t="n">
-        <v>10.01566223267491</v>
+        <v>9.811648683715475</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1103.682521513989</v>
+        <v>1076.084361206928</v>
       </c>
       <c r="I48" t="n">
-        <v>5952.291611803357</v>
+        <v>5901.747551908862</v>
       </c>
       <c r="J48" t="n">
-        <v>4.298214931583275</v>
+        <v>4.195228694614494</v>
       </c>
     </row>
     <row r="49">
@@ -1990,25 +1990,25 @@
         <v>233</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1856235176696469</v>
+        <v>0.1856235176696466</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1676857096888021</v>
+        <v>0.1676857096888018</v>
       </c>
       <c r="F49" t="n">
-        <v>10.3481717424932</v>
+        <v>10.34817174249318</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1136.107764509159</v>
+        <v>1136.107764509158</v>
       </c>
       <c r="I49" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J49" t="n">
-        <v>4.309345336910141</v>
+        <v>4.309345336910132</v>
       </c>
     </row>
   </sheetData>
